--- a/DuAn/exps/feature1/x_test.xlsx
+++ b/DuAn/exps/feature1/x_test.xlsx
@@ -475,7 +475,7 @@
         <v>-0.416638826785666</v>
       </c>
       <c r="D3" t="n">
-        <v>0.7006747654839023</v>
+        <v>0.7006747654839022</v>
       </c>
     </row>
     <row r="4">
@@ -489,7 +489,7 @@
         <v>1.753530399514071</v>
       </c>
       <c r="D4" t="n">
-        <v>0.04786486794437773</v>
+        <v>0.04786486794437766</v>
       </c>
     </row>
     <row r="5">
@@ -528,7 +528,7 @@
         <v>0.2861481336673205</v>
       </c>
       <c r="C7" t="n">
-        <v>-0.4813431201195148</v>
+        <v>-0.4813431201195149</v>
       </c>
       <c r="D7" t="n">
         <v>-1.255165329540716</v>
@@ -550,7 +550,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>0.1252653834638578</v>
+        <v>0.1252653834638579</v>
       </c>
       <c r="B9" t="n">
         <v>0.3387132565008774</v>
@@ -573,18 +573,18 @@
         <v>2.069850069972611</v>
       </c>
       <c r="D10" t="n">
-        <v>0.1057310603933853</v>
+        <v>0.1057310603933852</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>-0.1172297723465589</v>
+        <v>-0.1172297723465588</v>
       </c>
       <c r="B11" t="n">
         <v>0.7634340299111889</v>
       </c>
       <c r="C11" t="n">
-        <v>0.05525828725118422</v>
+        <v>0.05525828725118417</v>
       </c>
       <c r="D11" t="n">
         <v>0.179205235233922</v>
@@ -615,7 +615,7 @@
         <v>-1.036920910903664</v>
       </c>
       <c r="D13" t="n">
-        <v>0.1486479836252482</v>
+        <v>0.1486479836252481</v>
       </c>
     </row>
     <row r="14">
@@ -629,12 +629,12 @@
         <v>2.189274030437505</v>
       </c>
       <c r="D14" t="n">
-        <v>0.336557230394401</v>
+        <v>0.3365572303944009</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>-0.2681039951938008</v>
+        <v>-0.2681039951938007</v>
       </c>
       <c r="B15" t="n">
         <v>-0.454302069546095</v>
@@ -643,12 +643,12 @@
         <v>1.516267339886313</v>
       </c>
       <c r="D15" t="n">
-        <v>0.7910542356853674</v>
+        <v>0.7910542356853673</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>-0.02132880606734252</v>
+        <v>-0.02132880606734248</v>
       </c>
       <c r="B16" t="n">
         <v>1.427830764488811</v>
@@ -668,10 +668,10 @@
         <v>0.7119188547630961</v>
       </c>
       <c r="C17" t="n">
-        <v>0.1812780675465955</v>
+        <v>0.1812780675465954</v>
       </c>
       <c r="D17" t="n">
-        <v>0.5751848774187601</v>
+        <v>0.57518487741876</v>
       </c>
     </row>
     <row r="18">
@@ -685,7 +685,7 @@
         <v>-0.5450475524260522</v>
       </c>
       <c r="D18" t="n">
-        <v>0.08492376943457455</v>
+        <v>0.0849237694345745</v>
       </c>
     </row>
     <row r="19">
@@ -699,7 +699,7 @@
         <v>-0.7854873266930302</v>
       </c>
       <c r="D19" t="n">
-        <v>0.6122462930813782</v>
+        <v>0.6122462930813781</v>
       </c>
     </row>
     <row r="20">
@@ -724,7 +724,7 @@
         <v>0.5556290613897402</v>
       </c>
       <c r="C21" t="n">
-        <v>-0.4749523999869086</v>
+        <v>-0.4749523999869087</v>
       </c>
       <c r="D21" t="n">
         <v>-2.133617173548503</v>
@@ -741,7 +741,7 @@
         <v>0.4316861532676787</v>
       </c>
       <c r="D22" t="n">
-        <v>0.9659601826914741</v>
+        <v>0.965960182691474</v>
       </c>
     </row>
     <row r="23">
@@ -755,7 +755,7 @@
         <v>0.4404728107804159</v>
       </c>
       <c r="D23" t="n">
-        <v>0.2513770687602172</v>
+        <v>0.2513770687602171</v>
       </c>
     </row>
     <row r="24">
@@ -769,7 +769,7 @@
         <v>-1.050299004835524</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.8104082282099273</v>
+        <v>-0.8104082282099274</v>
       </c>
     </row>
     <row r="25">
@@ -780,10 +780,10 @@
         <v>0.2889592839219501</v>
       </c>
       <c r="C25" t="n">
-        <v>-0.1801915045927778</v>
+        <v>-0.1801915045927779</v>
       </c>
       <c r="D25" t="n">
-        <v>0.04006087674861308</v>
+        <v>0.04006087674861302</v>
       </c>
     </row>
     <row r="26">
@@ -794,7 +794,7 @@
         <v>-0.1014180393896328</v>
       </c>
       <c r="C26" t="n">
-        <v>-0.1831864263179415</v>
+        <v>-0.1831864263179416</v>
       </c>
       <c r="D26" t="n">
         <v>1.045302435963362</v>
@@ -802,7 +802,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>0.4694413796042136</v>
+        <v>0.4694413796042137</v>
       </c>
       <c r="B27" t="n">
         <v>0.3926839544617491</v>
@@ -811,7 +811,7 @@
         <v>-1.465276291345565</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.7161267624105798</v>
+        <v>-0.7161267624105799</v>
       </c>
     </row>
     <row r="28">
@@ -825,7 +825,7 @@
         <v>1.587562791693908</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.2232986843842308</v>
+        <v>-0.2232986843842309</v>
       </c>
     </row>
     <row r="29">
@@ -853,12 +853,12 @@
         <v>3.621336057526694</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.9840369756260056</v>
+        <v>-0.9840369756260057</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>0.2332643682127153</v>
+        <v>0.2332643682127154</v>
       </c>
       <c r="B31" t="n">
         <v>-0.07618542565831847</v>
@@ -867,12 +867,12 @@
         <v>-0.9758105236400115</v>
       </c>
       <c r="D31" t="n">
-        <v>0.5972919955193912</v>
+        <v>0.5972919955193911</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>0.397567478660024</v>
+        <v>0.3975674786600241</v>
       </c>
       <c r="B32" t="n">
         <v>-1.223134729547217</v>
@@ -892,10 +892,10 @@
         <v>-0.6421241627635498</v>
       </c>
       <c r="C33" t="n">
-        <v>0.03787142649653714</v>
+        <v>0.0378714264965371</v>
       </c>
       <c r="D33" t="n">
-        <v>0.9952201213307489</v>
+        <v>0.9952201213307488</v>
       </c>
     </row>
     <row r="34">
@@ -909,7 +909,7 @@
         <v>-0.4681608031720237</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.009996296159787088</v>
+        <v>-0.009996296159787149</v>
       </c>
     </row>
     <row r="35">
@@ -923,7 +923,7 @@
         <v>0.274528509744106</v>
       </c>
       <c r="D35" t="n">
-        <v>0.9412559244796238</v>
+        <v>0.9412559244796237</v>
       </c>
     </row>
     <row r="36">
@@ -934,7 +934,7 @@
         <v>-0.123844583258344</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.08772883168951257</v>
+        <v>-0.08772883168951261</v>
       </c>
       <c r="D36" t="n">
         <v>1.391202277688008</v>
@@ -948,10 +948,10 @@
         <v>1.041314539117322</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.4260244686434359</v>
+        <v>-0.426024468643436</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.7961277288568528</v>
+        <v>-0.7961277288568529</v>
       </c>
     </row>
     <row r="38">
@@ -970,16 +970,16 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>0.06443212198123575</v>
+        <v>0.06443212198123578</v>
       </c>
       <c r="B39" t="n">
         <v>-0.2811792439251375</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.07076149304422695</v>
+        <v>-0.07076149304422699</v>
       </c>
       <c r="D39" t="n">
-        <v>0.2591710032662966</v>
+        <v>0.2591710032662965</v>
       </c>
     </row>
     <row r="40">
@@ -993,7 +993,7 @@
         <v>-0.5917776540521479</v>
       </c>
       <c r="D40" t="n">
-        <v>0.2747890423475112</v>
+        <v>0.2747890423475111</v>
       </c>
     </row>
     <row r="41">
@@ -1007,7 +1007,7 @@
         <v>2.199249333926767</v>
       </c>
       <c r="D41" t="n">
-        <v>0.1284893491511371</v>
+        <v>0.128489349151137</v>
       </c>
     </row>
     <row r="42">
@@ -1018,7 +1018,7 @@
         <v>1.19304891430697</v>
       </c>
       <c r="C42" t="n">
-        <v>-0.3581261204231798</v>
+        <v>-0.3581261204231799</v>
       </c>
       <c r="D42" t="n">
         <v>-1.320181828355946</v>
@@ -1035,7 +1035,7 @@
         <v>-0.480142820751064</v>
       </c>
       <c r="D43" t="n">
-        <v>-0.2096215864122721</v>
+        <v>-0.2096215864122722</v>
       </c>
     </row>
     <row r="44">
@@ -1060,7 +1060,7 @@
         <v>1.556449355958161</v>
       </c>
       <c r="C45" t="n">
-        <v>0.1898549640046519</v>
+        <v>0.1898549640046518</v>
       </c>
       <c r="D45" t="n">
         <v>-1.177779102412611</v>
@@ -1077,7 +1077,7 @@
         <v>1.426419688131401</v>
       </c>
       <c r="D46" t="n">
-        <v>0.905494335958826</v>
+        <v>0.9054943359588259</v>
       </c>
     </row>
     <row r="47">
@@ -1091,7 +1091,7 @@
         <v>-0.9166812130038994</v>
       </c>
       <c r="D47" t="n">
-        <v>0.05826851342378304</v>
+        <v>0.05826851342378298</v>
       </c>
     </row>
     <row r="48">
@@ -1119,12 +1119,12 @@
         <v>1.594554826849932</v>
       </c>
       <c r="D49" t="n">
-        <v>0.2695847054353872</v>
+        <v>0.2695847054353871</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>0.03834081591380795</v>
+        <v>0.03834081591380798</v>
       </c>
       <c r="B50" t="n">
         <v>1.45446895334744</v>
@@ -1158,10 +1158,10 @@
         <v>-0.8303018834228553</v>
       </c>
       <c r="C52" t="n">
-        <v>0.2419689327008863</v>
+        <v>0.2419689327008862</v>
       </c>
       <c r="D52" t="n">
-        <v>0.6512612207153589</v>
+        <v>0.6512612207153587</v>
       </c>
     </row>
     <row r="53">
@@ -1172,21 +1172,21 @@
         <v>-0.3323489524154324</v>
       </c>
       <c r="C53" t="n">
-        <v>0.1367388036027207</v>
+        <v>0.1367388036027206</v>
       </c>
       <c r="D53" t="n">
-        <v>0.844369776051793</v>
+        <v>0.8443697760517929</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>-0.259916711276261</v>
+        <v>-0.2599167112762609</v>
       </c>
       <c r="B54" t="n">
         <v>0.4200164635639917</v>
       </c>
       <c r="C54" t="n">
-        <v>0.3655881142593958</v>
+        <v>0.3655881142593957</v>
       </c>
       <c r="D54" t="n">
         <v>0.3547648670695709</v>
@@ -1217,7 +1217,7 @@
         <v>-0.6692563956160531</v>
       </c>
       <c r="D56" t="n">
-        <v>0.6538608749989996</v>
+        <v>0.6538608749989995</v>
       </c>
     </row>
     <row r="57">
@@ -1228,7 +1228,7 @@
         <v>-0.3614341967667964</v>
       </c>
       <c r="C57" t="n">
-        <v>-0.2137416199497677</v>
+        <v>-0.2137416199497678</v>
       </c>
       <c r="D57" t="n">
         <v>1.104435771312713</v>
@@ -1242,10 +1242,10 @@
         <v>-0.7742312900910553</v>
       </c>
       <c r="C58" t="n">
-        <v>0.1523077352168014</v>
+        <v>0.1523077352168013</v>
       </c>
       <c r="D58" t="n">
-        <v>0.793653889969008</v>
+        <v>0.7936538899690079</v>
       </c>
     </row>
     <row r="59">
@@ -1259,7 +1259,7 @@
         <v>-0.952830034760545</v>
       </c>
       <c r="D59" t="n">
-        <v>-0.1029703923000503</v>
+        <v>-0.1029703923000504</v>
       </c>
     </row>
     <row r="60">
@@ -1273,7 +1273,7 @@
         <v>2.306483846436326</v>
       </c>
       <c r="D60" t="n">
-        <v>0.2546304078734</v>
+        <v>0.2546304078733999</v>
       </c>
     </row>
     <row r="61">
@@ -1287,12 +1287,12 @@
         <v>2.779798012931463</v>
       </c>
       <c r="D61" t="n">
-        <v>-0.7791822067371834</v>
+        <v>-0.7791822067371835</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>0.2934321951301246</v>
+        <v>0.2934321951301247</v>
       </c>
       <c r="B62" t="n">
         <v>0.4056389541291689</v>
@@ -1312,10 +1312,10 @@
         <v>-0.6586015675693007</v>
       </c>
       <c r="C63" t="n">
-        <v>-0.006458076392656855</v>
+        <v>-0.006458076392656904</v>
       </c>
       <c r="D63" t="n">
-        <v>0.8534761085617993</v>
+        <v>0.8534761085617992</v>
       </c>
     </row>
     <row r="64">
@@ -1326,15 +1326,15 @@
         <v>0.412649895125655</v>
       </c>
       <c r="C64" t="n">
-        <v>-0.4154408580956005</v>
+        <v>-0.4154408580956006</v>
       </c>
       <c r="D64" t="n">
-        <v>-0.5217309507944319</v>
+        <v>-0.521730950794432</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>0.09382621322050515</v>
+        <v>0.09382621322050518</v>
       </c>
       <c r="B65" t="n">
         <v>0.6004889229831978</v>
@@ -1343,7 +1343,7 @@
         <v>-0.1115017512199952</v>
       </c>
       <c r="D65" t="n">
-        <v>0.330055580512878</v>
+        <v>0.3300555805128779</v>
       </c>
     </row>
     <row r="66">
@@ -1371,7 +1371,7 @@
         <v>-0.8066498864319305</v>
       </c>
       <c r="D67" t="n">
-        <v>0.1089843995065681</v>
+        <v>0.108984399506568</v>
       </c>
     </row>
     <row r="68">
@@ -1432,13 +1432,13 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>-0.09211571442333104</v>
+        <v>-0.09211571442333101</v>
       </c>
       <c r="B72" t="n">
         <v>-0.239135612978336</v>
       </c>
       <c r="C72" t="n">
-        <v>-0.47055907123054</v>
+        <v>-0.4705590712305401</v>
       </c>
       <c r="D72" t="n">
         <v>1.029684396882148</v>
@@ -1452,10 +1452,10 @@
         <v>0.2251834293500509</v>
       </c>
       <c r="C73" t="n">
-        <v>-0.3135925433345653</v>
+        <v>-0.3135925433345654</v>
       </c>
       <c r="D73" t="n">
-        <v>0.5134146780339333</v>
+        <v>0.5134146780339331</v>
       </c>
     </row>
     <row r="74">
@@ -1469,7 +1469,7 @@
         <v>1.395654733444895</v>
       </c>
       <c r="D74" t="n">
-        <v>0.8385218109998123</v>
+        <v>0.8385218109998122</v>
       </c>
     </row>
     <row r="75">
@@ -1480,7 +1480,7 @@
         <v>0.8352707731650383</v>
       </c>
       <c r="C75" t="n">
-        <v>-0.2025590250568995</v>
+        <v>-0.2025590250568996</v>
       </c>
       <c r="D75" t="n">
         <v>-2.816969237662173</v>
@@ -1497,7 +1497,7 @@
         <v>-0.5452456600888061</v>
       </c>
       <c r="D76" t="n">
-        <v>0.7852012422885438</v>
+        <v>0.7852012422885437</v>
       </c>
     </row>
     <row r="77">
@@ -1525,21 +1525,21 @@
         <v>1.035588229693497</v>
       </c>
       <c r="D78" t="n">
-        <v>0.2487774144765765</v>
+        <v>0.2487774144765764</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>-0.3933032440706983</v>
+        <v>-0.3933032440706982</v>
       </c>
       <c r="B79" t="n">
         <v>-0.3326978060012479</v>
       </c>
       <c r="C79" t="n">
-        <v>-0.4599731300043192</v>
+        <v>-0.4599731300043193</v>
       </c>
       <c r="D79" t="n">
-        <v>0.6590601835662809</v>
+        <v>0.6590601835662808</v>
       </c>
     </row>
     <row r="80">
@@ -1572,7 +1572,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>0.07484913428482892</v>
+        <v>0.07484913428482895</v>
       </c>
       <c r="B82" t="n">
         <v>-0.1077261928224614</v>
@@ -1581,7 +1581,7 @@
         <v>-0.8759409548281313</v>
       </c>
       <c r="D82" t="n">
-        <v>0.5907898428033839</v>
+        <v>0.5907898428033838</v>
       </c>
     </row>
     <row r="83">
@@ -1592,10 +1592,10 @@
         <v>-0.4893398398884369</v>
       </c>
       <c r="C83" t="n">
-        <v>0.3386221653409955</v>
+        <v>0.3386221653409954</v>
       </c>
       <c r="D83" t="n">
-        <v>0.7247353955558957</v>
+        <v>0.7247353955558956</v>
       </c>
     </row>
     <row r="84">
@@ -1606,10 +1606,10 @@
         <v>0.1116366675591363</v>
       </c>
       <c r="C84" t="n">
-        <v>0.1323338214544254</v>
+        <v>0.1323338214544253</v>
       </c>
       <c r="D84" t="n">
-        <v>0.7182287173295301</v>
+        <v>0.71822871732953</v>
       </c>
     </row>
     <row r="85">
@@ -1620,10 +1620,10 @@
         <v>-0.1077261928224614</v>
       </c>
       <c r="C85" t="n">
-        <v>-0.426823891329608</v>
+        <v>-0.4268238913296081</v>
       </c>
       <c r="D85" t="n">
-        <v>0.1896088807133274</v>
+        <v>0.1896088807133273</v>
       </c>
     </row>
     <row r="86">
@@ -1634,7 +1634,7 @@
         <v>-0.0740855302873903</v>
       </c>
       <c r="C86" t="n">
-        <v>-0.2049549624370305</v>
+        <v>-0.2049549624370306</v>
       </c>
       <c r="D86" t="n">
         <v>1.017978410088501</v>
@@ -1651,12 +1651,12 @@
         <v>2.682329042856485</v>
       </c>
       <c r="D87" t="n">
-        <v>-0.8259960972220861</v>
+        <v>-0.8259960972220862</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>-0.04983797385339695</v>
+        <v>-0.04983797385339692</v>
       </c>
       <c r="B88" t="n">
         <v>-0.1799134831261351</v>
@@ -1665,7 +1665,7 @@
         <v>-0.8124532756114307</v>
       </c>
       <c r="D88" t="n">
-        <v>0.7630966383603341</v>
+        <v>0.763096638360334</v>
       </c>
     </row>
     <row r="89">
@@ -1679,7 +1679,7 @@
         <v>0.8694341676025061</v>
       </c>
       <c r="D89" t="n">
-        <v>0.3781718123120223</v>
+        <v>0.3781718123120222</v>
       </c>
     </row>
     <row r="90">
@@ -1704,7 +1704,7 @@
         <v>-0.3589803674180264</v>
       </c>
       <c r="C91" t="n">
-        <v>0.03689254157469375</v>
+        <v>0.0368925415746937</v>
       </c>
       <c r="D91" t="n">
         <v>1.418506190183499</v>
@@ -1721,7 +1721,7 @@
         <v>0.5660963757503191</v>
       </c>
       <c r="D92" t="n">
-        <v>0.723433054241654</v>
+        <v>0.7234330542416539</v>
       </c>
     </row>
     <row r="93">
@@ -1763,7 +1763,7 @@
         <v>1.687012838396427</v>
       </c>
       <c r="D95" t="n">
-        <v>-0.5210772659648897</v>
+        <v>-0.5210772659648898</v>
       </c>
     </row>
     <row r="96">
@@ -1777,7 +1777,7 @@
         <v>-1.329677422886401</v>
       </c>
       <c r="D96" t="n">
-        <v>-0.4326286801829953</v>
+        <v>-0.4326286801829954</v>
       </c>
     </row>
     <row r="97">
@@ -1824,7 +1824,7 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>-0.4685530931493968</v>
+        <v>-0.4685530931493967</v>
       </c>
       <c r="B100" t="n">
         <v>-0.261562326193448</v>
@@ -1833,12 +1833,12 @@
         <v>1.089520127530297</v>
       </c>
       <c r="D100" t="n">
-        <v>-0.2037887063948191</v>
+        <v>-0.2037887063948192</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>-0.03872417142916212</v>
+        <v>-0.0387241714291621</v>
       </c>
       <c r="B101" t="n">
         <v>1.284157277981112</v>
@@ -1861,7 +1861,7 @@
         <v>-0.1748006454874831</v>
       </c>
       <c r="D102" t="n">
-        <v>-0.01326472030749789</v>
+        <v>-0.01326472030749795</v>
       </c>
     </row>
     <row r="103">
@@ -1872,10 +1872,10 @@
         <v>-1.013568558456603</v>
       </c>
       <c r="C103" t="n">
-        <v>0.1035732501793121</v>
+        <v>0.103573250179312</v>
       </c>
       <c r="D103" t="n">
-        <v>0.919794948691271</v>
+        <v>0.9197949486912709</v>
       </c>
     </row>
     <row r="104">
@@ -1886,7 +1886,7 @@
         <v>1.673484653607231</v>
       </c>
       <c r="C104" t="n">
-        <v>0.06465092114411018</v>
+        <v>0.06465092114411014</v>
       </c>
       <c r="D104" t="n">
         <v>-2.160921086043994</v>
@@ -1894,7 +1894,7 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>-0.4182309106366545</v>
+        <v>-0.4182309106366544</v>
       </c>
       <c r="B105" t="n">
         <v>-1.248706036080294</v>
@@ -1903,7 +1903,7 @@
         <v>0.6633555847706168</v>
       </c>
       <c r="D105" t="n">
-        <v>0.7032744197675429</v>
+        <v>0.7032744197675428</v>
       </c>
     </row>
     <row r="106">
@@ -1931,7 +1931,7 @@
         <v>-0.5316671278158071</v>
       </c>
       <c r="D107" t="n">
-        <v>0.2468264166776354</v>
+        <v>0.2468264166776353</v>
       </c>
     </row>
     <row r="108">
@@ -1950,16 +1950,16 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>-0.438650345122059</v>
+        <v>-0.4386503451220589</v>
       </c>
       <c r="B109" t="n">
-        <v>0.003000951393779485</v>
+        <v>0.00300095139377948</v>
       </c>
       <c r="C109" t="n">
         <v>-0.8721652558438781</v>
       </c>
       <c r="D109" t="n">
-        <v>0.1492966401099477</v>
+        <v>0.1492966401099476</v>
       </c>
     </row>
     <row r="110">
@@ -1973,12 +1973,12 @@
         <v>0.5259620939547397</v>
       </c>
       <c r="D110" t="n">
-        <v>0.4659516282298467</v>
+        <v>0.4659516282298466</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>0.06540762815013411</v>
+        <v>0.06540762815013414</v>
       </c>
       <c r="B111" t="n">
         <v>1.279957487239256</v>
@@ -2001,7 +2001,7 @@
         <v>3.736961012223483</v>
       </c>
       <c r="D112" t="n">
-        <v>-0.7746566963788147</v>
+        <v>-0.7746566963788148</v>
       </c>
     </row>
     <row r="113">
@@ -2015,7 +2015,7 @@
         <v>0.2827091908766545</v>
       </c>
       <c r="D113" t="n">
-        <v>0.7026257632828433</v>
+        <v>0.7026257632828432</v>
       </c>
     </row>
     <row r="114">
@@ -2026,24 +2026,24 @@
         <v>0.1424746471596218</v>
       </c>
       <c r="C114" t="n">
-        <v>0.09140710900782982</v>
+        <v>0.09140710900782978</v>
       </c>
       <c r="D114" t="n">
-        <v>0.5212171607262451</v>
+        <v>0.521217160726245</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>-0.4351629105682473</v>
+        <v>-0.4351629105682472</v>
       </c>
       <c r="B115" t="n">
-        <v>0.0506719632418667</v>
+        <v>0.05067196324186669</v>
       </c>
       <c r="C115" t="n">
         <v>-0.9133017293451543</v>
       </c>
       <c r="D115" t="n">
-        <v>-0.006124470630960531</v>
+        <v>-0.006124470630960593</v>
       </c>
     </row>
     <row r="116">
@@ -2054,7 +2054,7 @@
         <v>0.01666720594490075</v>
       </c>
       <c r="C116" t="n">
-        <v>0.01290986098953043</v>
+        <v>0.01290986098953038</v>
       </c>
       <c r="D116" t="n">
         <v>1.028382055567906</v>
@@ -2062,13 +2062,13 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>-0.2098279534539337</v>
+        <v>-0.2098279534539336</v>
       </c>
       <c r="B117" t="n">
         <v>1.083363250456149</v>
       </c>
       <c r="C117" t="n">
-        <v>0.07903120678166684</v>
+        <v>0.07903120678166679</v>
       </c>
       <c r="D117" t="n">
         <v>-1.411848554837125</v>
@@ -2085,7 +2085,7 @@
         <v>-0.7499444813165734</v>
       </c>
       <c r="D118" t="n">
-        <v>-0.5048357121231889</v>
+        <v>-0.504835712123189</v>
       </c>
     </row>
     <row r="119">
@@ -2124,7 +2124,7 @@
         <v>0.4340383455569637</v>
       </c>
       <c r="C121" t="n">
-        <v>-0.4977184664549237</v>
+        <v>-0.4977184664549238</v>
       </c>
       <c r="D121" t="n">
         <v>-1.45152219564549</v>
@@ -2152,15 +2152,15 @@
         <v>-0.5180779241179942</v>
       </c>
       <c r="C123" t="n">
-        <v>0.3212586113702018</v>
+        <v>0.3212586113702017</v>
       </c>
       <c r="D123" t="n">
-        <v>0.8742833995206101</v>
+        <v>0.87428339952061</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>-0.4071171082124196</v>
+        <v>-0.4071171082124195</v>
       </c>
       <c r="B124" t="n">
         <v>1.646846464748602</v>
@@ -2180,10 +2180,10 @@
         <v>-0.3523216669353735</v>
       </c>
       <c r="C125" t="n">
-        <v>-0.3056053085080002</v>
+        <v>-0.3056053085080003</v>
       </c>
       <c r="D125" t="n">
-        <v>0.6818184723240327</v>
+        <v>0.6818184723240326</v>
       </c>
     </row>
     <row r="126">
@@ -2197,35 +2197,35 @@
         <v>1.791660297898257</v>
       </c>
       <c r="D126" t="n">
-        <v>0.140195335944784</v>
+        <v>0.1401953359447839</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>0.4372148365245358</v>
+        <v>0.4372148365245359</v>
       </c>
       <c r="B127" t="n">
         <v>0.323997054264292</v>
       </c>
       <c r="C127" t="n">
-        <v>-0.03479912555840864</v>
+        <v>-0.03479912555840869</v>
       </c>
       <c r="D127" t="n">
-        <v>0.3586618343226107</v>
+        <v>0.3586618343226106</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>-0.4472522191613806</v>
+        <v>-0.4472522191613805</v>
       </c>
       <c r="B128" t="n">
         <v>-1.036701276816989</v>
       </c>
       <c r="C128" t="n">
-        <v>0.1527039505423095</v>
+        <v>0.1527039505423094</v>
       </c>
       <c r="D128" t="n">
-        <v>0.7969072290821909</v>
+        <v>0.7969072290821908</v>
       </c>
     </row>
     <row r="129">
@@ -2244,7 +2244,7 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>0.2693580964619545</v>
+        <v>0.2693580964619546</v>
       </c>
       <c r="B130" t="n">
         <v>1.2358088805295</v>
@@ -2253,7 +2253,7 @@
         <v>-0.8451993069254778</v>
       </c>
       <c r="D130" t="n">
-        <v>-0.02498076379083007</v>
+        <v>-0.02498076379083013</v>
       </c>
     </row>
     <row r="131">
@@ -2272,16 +2272,16 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>-0.192481363400559</v>
+        <v>-0.1924813634005589</v>
       </c>
       <c r="B132" t="n">
         <v>0.7217240113741237</v>
       </c>
       <c r="C132" t="n">
-        <v>-0.2440963752404545</v>
+        <v>-0.2440963752404546</v>
       </c>
       <c r="D132" t="n">
-        <v>0.1896088807133274</v>
+        <v>0.1896088807133273</v>
       </c>
     </row>
     <row r="133">
@@ -2306,7 +2306,7 @@
         <v>-0.2598094215979257</v>
       </c>
       <c r="C134" t="n">
-        <v>-0.2313149349752421</v>
+        <v>-0.2313149349752422</v>
       </c>
       <c r="D134" t="n">
         <v>0.3931261098740094</v>
@@ -2328,16 +2328,16 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>0.3307104665844546</v>
+        <v>0.3307104665844547</v>
       </c>
       <c r="B136" t="n">
         <v>0.7592342391693326</v>
       </c>
       <c r="C136" t="n">
-        <v>-0.2518855024042656</v>
+        <v>-0.2518855024042657</v>
       </c>
       <c r="D136" t="n">
-        <v>0.7923565769996089</v>
+        <v>0.7923565769996088</v>
       </c>
     </row>
     <row r="137">
@@ -2365,7 +2365,7 @@
         <v>0.4560650491783501</v>
       </c>
       <c r="D138" t="n">
-        <v>0.4223860485132843</v>
+        <v>0.4223860485132842</v>
       </c>
     </row>
     <row r="139">
@@ -2379,7 +2379,7 @@
         <v>-0.4483919891075577</v>
       </c>
       <c r="D139" t="n">
-        <v>-0.7356367403999915</v>
+        <v>-0.7356367403999916</v>
       </c>
     </row>
     <row r="140">
@@ -2390,15 +2390,15 @@
         <v>0.3187473158369716</v>
       </c>
       <c r="C140" t="n">
-        <v>-0.1825874419729088</v>
+        <v>-0.1825874419729089</v>
       </c>
       <c r="D140" t="n">
-        <v>0.949708572160088</v>
+        <v>0.9497085721600879</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>0.3381312813692885</v>
+        <v>0.3381312813692886</v>
       </c>
       <c r="B141" t="n">
         <v>0.2672321406888788</v>
@@ -2407,7 +2407,7 @@
         <v>0.6527743049011667</v>
       </c>
       <c r="D141" t="n">
-        <v>0.9373539288817414</v>
+        <v>0.9373539288817413</v>
       </c>
     </row>
     <row r="142">
@@ -2421,7 +2421,7 @@
         <v>1.040995403547489</v>
       </c>
       <c r="D142" t="n">
-        <v>0.565431396927507</v>
+        <v>0.5654313969275069</v>
       </c>
     </row>
     <row r="143">
@@ -2435,7 +2435,7 @@
         <v>-1.044891830981532</v>
       </c>
       <c r="D143" t="n">
-        <v>-0.1023167074705081</v>
+        <v>-0.1023167074705082</v>
       </c>
     </row>
     <row r="144">
@@ -2446,7 +2446,7 @@
         <v>-0.3884161588192147</v>
       </c>
       <c r="C144" t="n">
-        <v>0.2653456369058609</v>
+        <v>0.2653456369058608</v>
       </c>
       <c r="D144" t="n">
         <v>1.142802042461994</v>
@@ -2454,21 +2454,21 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>-0.194620509070929</v>
+        <v>-0.1946205090709289</v>
       </c>
       <c r="B145" t="n">
         <v>-0.4770791604646305</v>
       </c>
       <c r="C145" t="n">
-        <v>-0.03820191600100717</v>
+        <v>-0.03820191600100722</v>
       </c>
       <c r="D145" t="n">
-        <v>0.9106936445261073</v>
+        <v>0.9106936445261072</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>0.2598469113151955</v>
+        <v>0.2598469113151956</v>
       </c>
       <c r="B146" t="n">
         <v>1.064447257477708</v>
@@ -2477,7 +2477,7 @@
         <v>-0.1055119077696677</v>
       </c>
       <c r="D146" t="n">
-        <v>-0.8884481401675737</v>
+        <v>-0.8884481401675738</v>
       </c>
     </row>
     <row r="147">
@@ -2491,7 +2491,7 @@
         <v>1.034795799042481</v>
       </c>
       <c r="D147" t="n">
-        <v>0.5810363623121307</v>
+        <v>0.5810363623121306</v>
       </c>
     </row>
     <row r="148">
@@ -2505,7 +2505,7 @@
         <v>-0.5368598792583477</v>
       </c>
       <c r="D148" t="n">
-        <v>0.3554135235542705</v>
+        <v>0.3554135235542704</v>
       </c>
     </row>
     <row r="149">
@@ -2547,7 +2547,7 @@
         <v>2.398965164766674</v>
       </c>
       <c r="D151" t="n">
-        <v>-0.4124650173640415</v>
+        <v>-0.4124650173640416</v>
       </c>
     </row>
     <row r="152">
@@ -2561,12 +2561,12 @@
         <v>0.9567180731335428</v>
       </c>
       <c r="D152" t="n">
-        <v>0.6402038904064115</v>
+        <v>0.6402038904064113</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>-0.425393913076851</v>
+        <v>-0.4253939130768509</v>
       </c>
       <c r="B153" t="n">
         <v>-0.1406657612578839</v>
@@ -2575,7 +2575,7 @@
         <v>-0.7427426851058684</v>
       </c>
       <c r="D153" t="n">
-        <v>0.4451443372710361</v>
+        <v>0.445144337271036</v>
       </c>
     </row>
     <row r="154">
@@ -2589,7 +2589,7 @@
         <v>-0.8192355497127741</v>
       </c>
       <c r="D154" t="n">
-        <v>0.555028254282586</v>
+        <v>0.5550282542825858</v>
       </c>
     </row>
     <row r="155">
@@ -2614,7 +2614,7 @@
         <v>0.2661821930034147</v>
       </c>
       <c r="C156" t="n">
-        <v>-0.3974666663878473</v>
+        <v>-0.3974666663878474</v>
       </c>
       <c r="D156" t="n">
         <v>0.4100314052349378</v>
@@ -2622,7 +2622,7 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>-0.2765212198511523</v>
+        <v>-0.2765212198511522</v>
       </c>
       <c r="B157" t="n">
         <v>-0.1851699954094908</v>
@@ -2631,7 +2631,7 @@
         <v>-0.483140073154613</v>
       </c>
       <c r="D157" t="n">
-        <v>0.8729810582063684</v>
+        <v>0.8729810582063683</v>
       </c>
     </row>
     <row r="158">
@@ -2645,7 +2645,7 @@
         <v>-0.7601295458605155</v>
       </c>
       <c r="D158" t="n">
-        <v>0.4223860485132843</v>
+        <v>0.4223860485132842</v>
       </c>
     </row>
     <row r="159">
@@ -2656,7 +2656,7 @@
         <v>1.331472662387348</v>
       </c>
       <c r="C159" t="n">
-        <v>0.2086169250066504</v>
+        <v>0.2086169250066503</v>
       </c>
       <c r="D159" t="n">
         <v>-2.10757034726367</v>
@@ -2673,7 +2673,7 @@
         <v>-0.3243765922235401</v>
       </c>
       <c r="D160" t="n">
-        <v>-0.2694588900395913</v>
+        <v>-0.2694588900395914</v>
       </c>
     </row>
     <row r="161">
@@ -2681,18 +2681,18 @@
         <v>-1.109519873275871</v>
       </c>
       <c r="B161" t="n">
-        <v>0.05627732911103786</v>
+        <v>0.05627732911103785</v>
       </c>
       <c r="C161" t="n">
         <v>-0.4589755996553931</v>
       </c>
       <c r="D161" t="n">
-        <v>-0.5204235811353476</v>
+        <v>-0.5204235811353477</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>0.305173108662937</v>
+        <v>0.3051731086629371</v>
       </c>
       <c r="B162" t="n">
         <v>0.4732759066411619</v>
@@ -2701,7 +2701,7 @@
         <v>-0.671051017972766</v>
       </c>
       <c r="D162" t="n">
-        <v>-0.33900089921319</v>
+        <v>-0.3390008992131901</v>
       </c>
     </row>
     <row r="163">
@@ -2715,12 +2715,12 @@
         <v>1.204935321172405</v>
       </c>
       <c r="D163" t="n">
-        <v>0.9158929530933887</v>
+        <v>0.9158929530933886</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>0.06052661335503914</v>
+        <v>0.06052661335503917</v>
       </c>
       <c r="B164" t="n">
         <v>-0.3295445760168381</v>
@@ -2729,7 +2729,7 @@
         <v>-0.3175873260870405</v>
       </c>
       <c r="D164" t="n">
-        <v>0.7663449491286743</v>
+        <v>0.7663449491286742</v>
       </c>
     </row>
     <row r="165">
@@ -2743,7 +2743,7 @@
         <v>1.845778650005885</v>
       </c>
       <c r="D165" t="n">
-        <v>0.3664658255183754</v>
+        <v>0.3664658255183753</v>
       </c>
     </row>
     <row r="166">
@@ -2762,7 +2762,7 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>-0.02207437149642913</v>
+        <v>-0.02207437149642909</v>
       </c>
       <c r="B167" t="n">
         <v>-0.429066068886763</v>
@@ -2771,15 +2771,15 @@
         <v>1.524867543128223</v>
       </c>
       <c r="D167" t="n">
-        <v>0.8898863535672967</v>
+        <v>0.8898863535672966</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>0.07484913428482892</v>
+        <v>0.07484913428482895</v>
       </c>
       <c r="B168" t="n">
-        <v>0.05031633580001596</v>
+        <v>0.05031633580001595</v>
       </c>
       <c r="C168" t="n">
         <v>-1.126768562658576</v>
@@ -2804,7 +2804,7 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>-0.06090648491979007</v>
+        <v>-0.06090648491979005</v>
       </c>
       <c r="B170" t="n">
         <v>1.320956250892619</v>
@@ -2813,7 +2813,7 @@
         <v>-0.3822899879460196</v>
       </c>
       <c r="D170" t="n">
-        <v>-0.3929550393746299</v>
+        <v>-0.39295503937463</v>
       </c>
     </row>
     <row r="171">
@@ -2827,7 +2827,7 @@
         <v>-1.071461564574424</v>
       </c>
       <c r="D171" t="n">
-        <v>-0.3207982908828627</v>
+        <v>-0.3207982908828628</v>
       </c>
     </row>
     <row r="172">
@@ -2841,18 +2841,18 @@
         <v>-0.881954105062312</v>
       </c>
       <c r="D172" t="n">
-        <v>0.7624479818756347</v>
+        <v>0.7624479818756346</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>0.130986030354326</v>
+        <v>0.1309860303543261</v>
       </c>
       <c r="B173" t="n">
         <v>0.7087690117067039</v>
       </c>
       <c r="C173" t="n">
-        <v>-0.08152922718450437</v>
+        <v>-0.08152922718450441</v>
       </c>
       <c r="D173" t="n">
         <v>0.216917821553661</v>
@@ -2866,15 +2866,15 @@
         <v>-0.5489159037184799</v>
       </c>
       <c r="C174" t="n">
-        <v>-0.04218737603994099</v>
+        <v>-0.04218737603994104</v>
       </c>
       <c r="D174" t="n">
-        <v>0.6246009363597248</v>
+        <v>0.6246009363597247</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>-0.3442840590835559</v>
+        <v>-0.3442840590835558</v>
       </c>
       <c r="B175" t="n">
         <v>0.01492293801582332</v>
@@ -2902,16 +2902,16 @@
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>0.2683129112809919</v>
+        <v>0.268312911280992</v>
       </c>
       <c r="B177" t="n">
         <v>0.8068883163773316</v>
       </c>
       <c r="C177" t="n">
-        <v>0.001139935143556201</v>
+        <v>0.001139935143556153</v>
       </c>
       <c r="D177" t="n">
-        <v>0.8918373513662379</v>
+        <v>0.8918373513662378</v>
       </c>
     </row>
     <row r="178">
@@ -2925,7 +2925,7 @@
         <v>-0.6766446460975855</v>
       </c>
       <c r="D178" t="n">
-        <v>-0.7564540880484873</v>
+        <v>-0.7564540880484875</v>
       </c>
     </row>
     <row r="179">
@@ -2944,13 +2944,13 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>-0.4539030808629054</v>
+        <v>-0.4539030808629053</v>
       </c>
       <c r="B180" t="n">
         <v>1.41452013737954</v>
       </c>
       <c r="C180" t="n">
-        <v>-0.0851417786817836</v>
+        <v>-0.08514177868178364</v>
       </c>
       <c r="D180" t="n">
         <v>-2.086149598234058</v>
@@ -2967,7 +2967,7 @@
         <v>1.992751228985516</v>
       </c>
       <c r="D181" t="n">
-        <v>0.03158811568877843</v>
+        <v>0.03158811568877837</v>
       </c>
     </row>
     <row r="182">
@@ -2986,7 +2986,7 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>-0.04156010722017377</v>
+        <v>-0.04156010722017374</v>
       </c>
       <c r="B183" t="n">
         <v>-0.152929827609708</v>
@@ -2995,7 +2995,7 @@
         <v>-0.5184871415467012</v>
       </c>
       <c r="D183" t="n">
-        <v>0.5595794091996522</v>
+        <v>0.5595794091996521</v>
       </c>
     </row>
     <row r="184">
@@ -3006,7 +3006,7 @@
         <v>-0.09195157558036791</v>
       </c>
       <c r="C184" t="n">
-        <v>-0.4429987993238775</v>
+        <v>-0.4429987993238776</v>
       </c>
       <c r="D184" t="n">
         <v>0.2403247667961123</v>
@@ -3014,7 +3014,7 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>-0.4867985424583993</v>
+        <v>-0.4867985424583992</v>
       </c>
       <c r="B185" t="n">
         <v>-0.3092196209830639</v>
@@ -3023,7 +3023,7 @@
         <v>-0.5714075249642638</v>
       </c>
       <c r="D185" t="n">
-        <v>0.5433242788268762</v>
+        <v>0.5433242788268761</v>
       </c>
     </row>
     <row r="186">
@@ -3037,7 +3037,7 @@
         <v>3.740154041611401</v>
       </c>
       <c r="D186" t="n">
-        <v>-0.8546073793766613</v>
+        <v>-0.8546073793766614</v>
       </c>
     </row>
     <row r="187">
@@ -3051,12 +3051,12 @@
         <v>0.7034898665661963</v>
       </c>
       <c r="D187" t="n">
-        <v>0.887286699283656</v>
+        <v>0.8872866992836559</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>0.2771273063071092</v>
+        <v>0.2771273063071093</v>
       </c>
       <c r="B188" t="n">
         <v>1.142939314286192</v>
@@ -3065,7 +3065,7 @@
         <v>-0.8396056788006584</v>
       </c>
       <c r="D188" t="n">
-        <v>0.0875284520630579</v>
+        <v>0.08752845206305784</v>
       </c>
     </row>
     <row r="189">
@@ -3090,7 +3090,7 @@
         <v>-0.08880173252397566</v>
       </c>
       <c r="C190" t="n">
-        <v>0.04586565335825826</v>
+        <v>0.04586565335825821</v>
       </c>
       <c r="D190" t="n">
         <v>1.215009074402188</v>
@@ -3121,7 +3121,7 @@
         <v>-1.100222135849537</v>
       </c>
       <c r="D192" t="n">
-        <v>-0.9645269976365938</v>
+        <v>-0.9645269976365939</v>
       </c>
     </row>
     <row r="193">
@@ -3140,7 +3140,7 @@
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>0.10214937121157</v>
+        <v>0.1021493712115701</v>
       </c>
       <c r="B194" t="n">
         <v>0.4207107838076051</v>
@@ -3174,10 +3174,10 @@
         <v>0.2300775403355206</v>
       </c>
       <c r="C196" t="n">
-        <v>-0.1618187668811313</v>
+        <v>-0.1618187668811314</v>
       </c>
       <c r="D196" t="n">
-        <v>0.6961241134013204</v>
+        <v>0.6961241134013203</v>
       </c>
     </row>
     <row r="197">
@@ -3196,7 +3196,7 @@
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>-0.06788483797801652</v>
+        <v>-0.06788483797801649</v>
       </c>
       <c r="B198" t="n">
         <v>1.269102382942764</v>
@@ -3216,10 +3216,10 @@
         <v>0.3075196494585411</v>
       </c>
       <c r="C199" t="n">
-        <v>-0.2047545240958911</v>
+        <v>-0.2047545240958912</v>
       </c>
       <c r="D199" t="n">
-        <v>0.06541881979000555</v>
+        <v>0.06541881979000549</v>
       </c>
     </row>
     <row r="200">
@@ -3233,7 +3233,7 @@
         <v>-1.184103250937975</v>
       </c>
       <c r="D200" t="n">
-        <v>-0.0691799149575642</v>
+        <v>-0.06917991495756426</v>
       </c>
     </row>
     <row r="201">
@@ -3247,12 +3247,12 @@
         <v>-0.9859955881839536</v>
       </c>
       <c r="D201" t="n">
-        <v>0.07647112175411039</v>
+        <v>0.07647112175411033</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>-0.3527500590493523</v>
+        <v>-0.3527500590493522</v>
       </c>
       <c r="B202" t="n">
         <v>-1.34403112513638</v>
@@ -3280,7 +3280,7 @@
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>-0.01825944558591591</v>
+        <v>-0.01825944558591588</v>
       </c>
       <c r="B204" t="n">
         <v>0.2836926108545416</v>
@@ -3331,7 +3331,7 @@
         <v>2.294317705264843</v>
       </c>
       <c r="D207" t="n">
-        <v>0.4997602076137664</v>
+        <v>0.4997602076137663</v>
       </c>
     </row>
     <row r="208">
@@ -3345,7 +3345,7 @@
         <v>-0.5296697364395695</v>
       </c>
       <c r="D208" t="n">
-        <v>-0.04770888247952616</v>
+        <v>-0.04770888247952622</v>
       </c>
     </row>
     <row r="209">
@@ -3356,10 +3356,10 @@
         <v>-0.7521654540562214</v>
       </c>
       <c r="C209" t="n">
-        <v>0.1085842087077962</v>
+        <v>0.1085842087077961</v>
       </c>
       <c r="D209" t="n">
-        <v>0.880785049402133</v>
+        <v>0.8807850494021329</v>
       </c>
     </row>
     <row r="210">
@@ -3370,24 +3370,24 @@
         <v>0.02403377438323751</v>
       </c>
       <c r="C210" t="n">
-        <v>-0.1883791777604822</v>
+        <v>-0.1883791777604823</v>
       </c>
       <c r="D210" t="n">
-        <v>0.3137989416366492</v>
+        <v>0.3137989416366491</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>0.3841891083437037</v>
+        <v>0.3841891083437038</v>
       </c>
       <c r="B211" t="n">
         <v>0.3373076813735626</v>
       </c>
       <c r="C211" t="n">
-        <v>0.4107333545834593</v>
+        <v>0.4107333545834592</v>
       </c>
       <c r="D211" t="n">
-        <v>0.7878059249170272</v>
+        <v>0.7878059249170271</v>
       </c>
     </row>
     <row r="212">
@@ -3401,7 +3401,7 @@
         <v>1.119469344781935</v>
       </c>
       <c r="D212" t="n">
-        <v>0.5979406520040906</v>
+        <v>0.5979406520040905</v>
       </c>
     </row>
     <row r="213">
@@ -3412,10 +3412,10 @@
         <v>-0.150828238774771</v>
       </c>
       <c r="C213" t="n">
-        <v>-0.1662120956374999</v>
+        <v>-0.1662120956375</v>
       </c>
       <c r="D213" t="n">
-        <v>0.9204486335208131</v>
+        <v>0.920448633520813</v>
       </c>
     </row>
     <row r="214">
@@ -3443,7 +3443,7 @@
         <v>1.741131190504055</v>
       </c>
       <c r="D215" t="n">
-        <v>0.5920901727796885</v>
+        <v>0.5920901727796883</v>
       </c>
     </row>
     <row r="216">
@@ -3468,10 +3468,10 @@
         <v>0.3776121247833131</v>
       </c>
       <c r="C217" t="n">
-        <v>-0.4380064862224762</v>
+        <v>-0.4380064862224763</v>
       </c>
       <c r="D217" t="n">
-        <v>-0.101663022640966</v>
+        <v>-0.1016630226409661</v>
       </c>
     </row>
     <row r="218">
@@ -3485,12 +3485,12 @@
         <v>-0.9216921715323836</v>
       </c>
       <c r="D218" t="n">
-        <v>0.5134146780339333</v>
+        <v>0.5134146780339331</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>0.05647826275411094</v>
+        <v>0.05647826275411097</v>
       </c>
       <c r="B219" t="n">
         <v>1.480057194520605</v>
@@ -3518,7 +3518,7 @@
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>-0.01742329744114589</v>
+        <v>-0.01742329744114586</v>
       </c>
       <c r="B221" t="n">
         <v>0.8808249550021092</v>
@@ -3555,7 +3555,7 @@
         <v>-1.131359999077699</v>
       </c>
       <c r="D223" t="n">
-        <v>-0.8643623683713672</v>
+        <v>-0.8643623683713673</v>
       </c>
     </row>
     <row r="224">
@@ -3569,12 +3569,12 @@
         <v>-1.117189474494823</v>
       </c>
       <c r="D224" t="n">
-        <v>-0.1894579235933183</v>
+        <v>-0.1894579235933184</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>0.001553781494530339</v>
+        <v>0.00155378149453037</v>
       </c>
       <c r="B225" t="n">
         <v>-0.3011604257651226</v>
@@ -3583,7 +3583,7 @@
         <v>-0.3677118277135475</v>
       </c>
       <c r="D225" t="n">
-        <v>0.7182287173295301</v>
+        <v>0.71822871732953</v>
       </c>
     </row>
     <row r="226">
@@ -3591,10 +3591,10 @@
         <v>1.105715278268166</v>
       </c>
       <c r="B226" t="n">
-        <v>-0.05550823011071118</v>
+        <v>-0.05550823011071119</v>
       </c>
       <c r="C226" t="n">
-        <v>-0.05936447573990736</v>
+        <v>-0.05936447573990741</v>
       </c>
       <c r="D226" t="n">
         <v>1.374307039016765</v>
@@ -3625,7 +3625,7 @@
         <v>0.8878232200628502</v>
       </c>
       <c r="D228" t="n">
-        <v>0.946455233046905</v>
+        <v>0.9464552330469049</v>
       </c>
     </row>
     <row r="229">
@@ -3650,10 +3650,10 @@
         <v>0.9551172210687374</v>
       </c>
       <c r="C230" t="n">
-        <v>-0.09213381383780785</v>
+        <v>-0.09213381383780789</v>
       </c>
       <c r="D230" t="n">
-        <v>0.2708870467496289</v>
+        <v>0.2708870467496288</v>
       </c>
     </row>
     <row r="231">
@@ -3667,7 +3667,7 @@
         <v>-0.5510373958763797</v>
       </c>
       <c r="D231" t="n">
-        <v>0.7826015880049032</v>
+        <v>0.7826015880049031</v>
       </c>
     </row>
     <row r="232">
@@ -3681,7 +3681,7 @@
         <v>-1.090643047685784</v>
       </c>
       <c r="D232" t="n">
-        <v>-0.7291501755529963</v>
+        <v>-0.7291501755529964</v>
       </c>
     </row>
     <row r="233">
@@ -3695,7 +3695,7 @@
         <v>2.083437924959151</v>
       </c>
       <c r="D233" t="n">
-        <v>0.330055580512878</v>
+        <v>0.3300555805128779</v>
       </c>
     </row>
     <row r="234">
@@ -3709,12 +3709,12 @@
         <v>0.3098849008497356</v>
       </c>
       <c r="D234" t="n">
-        <v>0.5855880200636812</v>
+        <v>0.585588020063681</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="n">
-        <v>0.3916796021406018</v>
+        <v>0.3916796021406019</v>
       </c>
       <c r="B235" t="n">
         <v>-0.2703229542038397</v>
@@ -3723,7 +3723,7 @@
         <v>1.092503395863535</v>
       </c>
       <c r="D235" t="n">
-        <v>0.3892241142761271</v>
+        <v>0.389224114276127</v>
       </c>
     </row>
     <row r="236">
@@ -3748,10 +3748,10 @@
         <v>-0.9158048812278259</v>
       </c>
       <c r="C237" t="n">
-        <v>0.3116795232064485</v>
+        <v>0.3116795232064484</v>
       </c>
       <c r="D237" t="n">
-        <v>0.5517769265073403</v>
+        <v>0.5517769265073402</v>
       </c>
     </row>
     <row r="238">
@@ -3779,7 +3779,7 @@
         <v>-0.2301169662851766</v>
       </c>
       <c r="D239" t="n">
-        <v>0.3196519350334727</v>
+        <v>0.3196519350334726</v>
       </c>
     </row>
     <row r="240">
@@ -3793,7 +3793,7 @@
         <v>0.9814698775858689</v>
       </c>
       <c r="D240" t="n">
-        <v>0.9809144802534613</v>
+        <v>0.9809144802534612</v>
       </c>
     </row>
     <row r="241">
@@ -3807,7 +3807,7 @@
         <v>-0.2015591640295881</v>
       </c>
       <c r="D241" t="n">
-        <v>-0.004817100971876279</v>
+        <v>-0.00481710097187634</v>
       </c>
     </row>
     <row r="242">
@@ -3818,7 +3818,7 @@
         <v>-0.3666890155861434</v>
       </c>
       <c r="C242" t="n">
-        <v>-0.2426979682092496</v>
+        <v>-0.2426979682092497</v>
       </c>
       <c r="D242" t="n">
         <v>1.097949206465718</v>
@@ -3835,7 +3835,7 @@
         <v>0.4223168261586062</v>
       </c>
       <c r="D243" t="n">
-        <v>0.5387728222091195</v>
+        <v>0.5387728222091194</v>
       </c>
     </row>
     <row r="244">
@@ -3846,10 +3846,10 @@
         <v>-0.3018615198647712</v>
       </c>
       <c r="C244" t="n">
-        <v>-0.1730036924523848</v>
+        <v>-0.1730036924523849</v>
       </c>
       <c r="D244" t="n">
-        <v>0.6883201222055558</v>
+        <v>0.6883201222055557</v>
       </c>
     </row>
     <row r="245">
@@ -3863,7 +3863,7 @@
         <v>-0.526273938032127</v>
       </c>
       <c r="D245" t="n">
-        <v>0.1200367014706729</v>
+        <v>0.1200367014706728</v>
       </c>
     </row>
     <row r="246">
@@ -3877,7 +3877,7 @@
         <v>-0.1136925889022161</v>
       </c>
       <c r="D246" t="n">
-        <v>0.7468399994841054</v>
+        <v>0.7468399994841053</v>
       </c>
     </row>
     <row r="247">
@@ -3896,7 +3896,7 @@
     </row>
     <row r="248">
       <c r="A248" t="n">
-        <v>-0.408510688453703</v>
+        <v>-0.4085106884537029</v>
       </c>
       <c r="B248" t="n">
         <v>1.343039021567541</v>
@@ -3919,21 +3919,21 @@
         <v>0.1918593474160455</v>
       </c>
       <c r="D249" t="n">
-        <v>0.9210972900055125</v>
+        <v>0.9210972900055124</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="n">
-        <v>-0.0190050110150025</v>
+        <v>-0.01900501101500247</v>
       </c>
       <c r="B250" t="n">
         <v>0.4974585726870122</v>
       </c>
       <c r="C250" t="n">
-        <v>0.1191654885772463</v>
+        <v>0.1191654885772462</v>
       </c>
       <c r="D250" t="n">
-        <v>0.4464416502404351</v>
+        <v>0.446441650240435</v>
       </c>
     </row>
     <row r="251">
@@ -3944,10 +3944,10 @@
         <v>-0.3050147498491811</v>
       </c>
       <c r="C251" t="n">
-        <v>-0.2544818781255359</v>
+        <v>-0.254481878125536</v>
       </c>
       <c r="D251" t="n">
-        <v>0.7995068833658315</v>
+        <v>0.7995068833658314</v>
       </c>
     </row>
     <row r="252">
@@ -3961,7 +3961,7 @@
         <v>0.7056807042484173</v>
       </c>
       <c r="D252" t="n">
-        <v>0.7812992466906615</v>
+        <v>0.7812992466906614</v>
       </c>
     </row>
     <row r="253">
@@ -4008,7 +4008,7 @@
     </row>
     <row r="256">
       <c r="A256" t="n">
-        <v>0.2239273805961168</v>
+        <v>0.2239273805961169</v>
       </c>
       <c r="B256" t="n">
         <v>1.377026844224419</v>
@@ -4017,12 +4017,12 @@
         <v>-0.6792550058891678</v>
       </c>
       <c r="D256" t="n">
-        <v>-0.3558961378844331</v>
+        <v>-0.3558961378844332</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="n">
-        <v>0.04610654180835951</v>
+        <v>0.04610654180835954</v>
       </c>
       <c r="B257" t="n">
         <v>-0.2331780065953317</v>
@@ -4042,10 +4042,10 @@
         <v>-0.6309134310252074</v>
       </c>
       <c r="C258" t="n">
-        <v>0.008924400950596604</v>
+        <v>0.008924400950596555</v>
       </c>
       <c r="D258" t="n">
-        <v>0.8996413425620026</v>
+        <v>0.8996413425620025</v>
       </c>
     </row>
     <row r="259">
@@ -4059,7 +4059,7 @@
         <v>2.426117567955901</v>
       </c>
       <c r="D259" t="n">
-        <v>-0.5444590694831279</v>
+        <v>-0.5444590694831281</v>
       </c>
     </row>
     <row r="260">
@@ -4070,10 +4070,10 @@
         <v>-0.5632764785132144</v>
       </c>
       <c r="C260" t="n">
-        <v>0.2266097621414862</v>
+        <v>0.2266097621414861</v>
       </c>
       <c r="D260" t="n">
-        <v>0.8014578811647727</v>
+        <v>0.8014578811647726</v>
       </c>
     </row>
     <row r="261">
@@ -4084,7 +4084,7 @@
         <v>-0.2549034563643943</v>
       </c>
       <c r="C261" t="n">
-        <v>-0.3675120885759237</v>
+        <v>-0.3675120885759238</v>
       </c>
       <c r="D261" t="n">
         <v>0.3638661712347346</v>
@@ -4101,18 +4101,18 @@
         <v>-0.5456465367710849</v>
       </c>
       <c r="D262" t="n">
-        <v>-0.06852623012802203</v>
+        <v>-0.06852623012802209</v>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="n">
-        <v>-0.002041655527980741</v>
+        <v>-0.00204165552798071</v>
       </c>
       <c r="B263" t="n">
         <v>-0.1567773778377312</v>
       </c>
       <c r="C263" t="n">
-        <v>-0.1837760879494329</v>
+        <v>-0.183776087949433</v>
       </c>
       <c r="D263" t="n">
         <v>0.3183546220640736</v>
@@ -4129,7 +4129,7 @@
         <v>1.019017106373719</v>
       </c>
       <c r="D264" t="n">
-        <v>0.7312370454374186</v>
+        <v>0.7312370454374185</v>
       </c>
     </row>
     <row r="265">
@@ -4140,7 +4140,7 @@
         <v>0.735390265925245</v>
       </c>
       <c r="C265" t="n">
-        <v>-0.08194874929386584</v>
+        <v>-0.08194874929386588</v>
       </c>
       <c r="D265" t="n">
         <v>0.3645148277194341</v>
@@ -4148,7 +4148,7 @@
     </row>
     <row r="266">
       <c r="A266" t="n">
-        <v>-0.04197818129255877</v>
+        <v>-0.04197818129255874</v>
       </c>
       <c r="B266" t="n">
         <v>0.1305695951776661</v>
@@ -4171,12 +4171,12 @@
         <v>0.2707295039759995</v>
       </c>
       <c r="D267" t="n">
-        <v>0.4581476370340821</v>
+        <v>0.458147637034082</v>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="n">
-        <v>-0.4458586389200972</v>
+        <v>-0.4458586389200971</v>
       </c>
       <c r="B268" t="n">
         <v>0.2647766178760999</v>
@@ -4185,7 +4185,7 @@
         <v>-0.7848813503128415</v>
       </c>
       <c r="D268" t="n">
-        <v>-0.939133856181303</v>
+        <v>-0.9391338561813031</v>
       </c>
     </row>
     <row r="269">
@@ -4199,7 +4199,7 @@
         <v>0.3194639890134888</v>
       </c>
       <c r="D269" t="n">
-        <v>0.5075626903060783</v>
+        <v>0.5075626903060781</v>
       </c>
     </row>
     <row r="270">
@@ -4210,7 +4210,7 @@
         <v>-0.1410163083077083</v>
       </c>
       <c r="C270" t="n">
-        <v>0.02130030317675959</v>
+        <v>0.02130030317675954</v>
       </c>
       <c r="D270" t="n">
         <v>1.138930216933167</v>
@@ -4232,13 +4232,13 @@
     </row>
     <row r="272">
       <c r="A272" t="n">
-        <v>-0.4042323971129631</v>
+        <v>-0.404232397112963</v>
       </c>
       <c r="B272" t="n">
         <v>-0.5948087783573133</v>
       </c>
       <c r="C272" t="n">
-        <v>0.1996438132230859</v>
+        <v>0.1996438132230858</v>
       </c>
       <c r="D272" t="n">
         <v>1.110972619608134</v>
@@ -4255,7 +4255,7 @@
         <v>0.5091812095802813</v>
       </c>
       <c r="D273" t="n">
-        <v>0.4867538908438148</v>
+        <v>0.4867538908438147</v>
       </c>
     </row>
     <row r="274">
@@ -4280,10 +4280,10 @@
         <v>-0.2535029616291059</v>
       </c>
       <c r="C275" t="n">
-        <v>-0.4060552162378305</v>
+        <v>-0.4060552162378306</v>
       </c>
       <c r="D275" t="n">
-        <v>0.5459251399132791</v>
+        <v>0.545925139913279</v>
       </c>
     </row>
     <row r="276">
@@ -4294,7 +4294,7 @@
         <v>-0.7276271605685204</v>
       </c>
       <c r="C276" t="n">
-        <v>0.3006787212276369</v>
+        <v>0.3006787212276368</v>
       </c>
       <c r="D276" t="n">
         <v>1.144763096950621</v>
@@ -4311,7 +4311,7 @@
         <v>-0.9226943632380803</v>
       </c>
       <c r="D277" t="n">
-        <v>-0.6771068064317566</v>
+        <v>-0.6771068064317567</v>
       </c>
     </row>
     <row r="278">
@@ -4358,13 +4358,13 @@
     </row>
     <row r="281">
       <c r="A281" t="n">
-        <v>0.06405933926669245</v>
+        <v>0.06405933926669248</v>
       </c>
       <c r="B281" t="n">
         <v>1.015031977700543</v>
       </c>
       <c r="C281" t="n">
-        <v>0.006920017539202935</v>
+        <v>0.006920017539202886</v>
       </c>
       <c r="D281" t="n">
         <v>-1.078972126254895</v>
@@ -4372,7 +4372,7 @@
     </row>
     <row r="282">
       <c r="A282" t="n">
-        <v>-0.4764616610186799</v>
+        <v>-0.4764616610186798</v>
       </c>
       <c r="B282" t="n">
         <v>0.1964453451204935</v>
@@ -4381,7 +4381,7 @@
         <v>-0.6478840748224721</v>
       </c>
       <c r="D282" t="n">
-        <v>-0.2460268030729268</v>
+        <v>-0.2460268030729269</v>
       </c>
     </row>
     <row r="283">
@@ -4392,10 +4392,10 @@
         <v>0.3506352431229213</v>
       </c>
       <c r="C283" t="n">
-        <v>-0.1961683049242933</v>
+        <v>-0.1961683049242934</v>
       </c>
       <c r="D283" t="n">
-        <v>0.7188824021590723</v>
+        <v>0.7188824021590722</v>
       </c>
     </row>
     <row r="284">
@@ -4428,7 +4428,7 @@
     </row>
     <row r="286">
       <c r="A286" t="n">
-        <v>0.4123045897115956</v>
+        <v>0.4123045897115957</v>
       </c>
       <c r="B286" t="n">
         <v>0.7977774800099174</v>
@@ -4437,7 +4437,7 @@
         <v>-0.4028598561715275</v>
       </c>
       <c r="D286" t="n">
-        <v>-0.6699665567552192</v>
+        <v>-0.6699665567552193</v>
       </c>
     </row>
     <row r="287">
@@ -4451,7 +4451,7 @@
         <v>0.7837584301573552</v>
       </c>
       <c r="D287" t="n">
-        <v>0.818363176525701</v>
+        <v>0.8183631765257009</v>
       </c>
     </row>
     <row r="288">
@@ -4465,7 +4465,7 @@
         <v>1.669439523370953</v>
       </c>
       <c r="D288" t="n">
-        <v>0.4327896939926896</v>
+        <v>0.4327896939926895</v>
       </c>
     </row>
     <row r="289">
@@ -4479,12 +4479,12 @@
         <v>-0.6922368844955196</v>
       </c>
       <c r="D289" t="n">
-        <v>0.8456721173660346</v>
+        <v>0.8456721173660345</v>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="n">
-        <v>-0.208897738642877</v>
+        <v>-0.2088977386428769</v>
       </c>
       <c r="B290" t="n">
         <v>-0.3926210299530975</v>
@@ -4535,7 +4535,7 @@
         <v>0.9920511574553189</v>
       </c>
       <c r="D293" t="n">
-        <v>0.7006747654839023</v>
+        <v>0.7006747654839022</v>
       </c>
     </row>
     <row r="294">
@@ -4549,21 +4549,21 @@
         <v>-0.8194453107674549</v>
       </c>
       <c r="D294" t="n">
-        <v>0.8710300604074271</v>
+        <v>0.871030060407427</v>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="n">
-        <v>-0.06862691945649992</v>
+        <v>-0.06862691945649989</v>
       </c>
       <c r="B295" t="n">
         <v>-0.1581863398930637</v>
       </c>
       <c r="C295" t="n">
-        <v>-0.4795438364060312</v>
+        <v>-0.4795438364060313</v>
       </c>
       <c r="D295" t="n">
-        <v>0.5446247093700776</v>
+        <v>0.5446247093700775</v>
       </c>
     </row>
     <row r="296">
@@ -4577,7 +4577,7 @@
         <v>-0.8761507158828119</v>
       </c>
       <c r="D296" t="n">
-        <v>0.1362933403469017</v>
+        <v>0.1362933403469016</v>
       </c>
     </row>
     <row r="297">
@@ -4588,10 +4588,10 @@
         <v>0.976488736859958</v>
       </c>
       <c r="C297" t="n">
-        <v>-0.3435478203500045</v>
+        <v>-0.3435478203500046</v>
       </c>
       <c r="D297" t="n">
-        <v>-0.7304575452120805</v>
+        <v>-0.7304575452120806</v>
       </c>
     </row>
     <row r="298">
@@ -4602,10 +4602,10 @@
         <v>-0.7146552262610124</v>
       </c>
       <c r="C298" t="n">
-        <v>0.1596959856983338</v>
+        <v>0.1596959856983337</v>
       </c>
       <c r="D298" t="n">
-        <v>0.697426454715562</v>
+        <v>0.6974264547155619</v>
       </c>
     </row>
     <row r="299">
@@ -4616,7 +4616,7 @@
         <v>0.7774559119041609</v>
       </c>
       <c r="C299" t="n">
-        <v>-0.3317648427050724</v>
+        <v>-0.3317648427050725</v>
       </c>
       <c r="D299" t="n">
         <v>-0.1855860980644919</v>
@@ -4630,15 +4630,15 @@
         <v>0.1466744379014782</v>
       </c>
       <c r="C300" t="n">
-        <v>-0.005642338957787341</v>
+        <v>-0.00564233895778739</v>
       </c>
       <c r="D300" t="n">
-        <v>0.9958738061602911</v>
+        <v>0.995873806160291</v>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="n">
-        <v>0.2638534545088852</v>
+        <v>0.2638534545088853</v>
       </c>
       <c r="B301" t="n">
         <v>-0.1357597960243526</v>
@@ -4647,7 +4647,7 @@
         <v>0.9111766174839712</v>
       </c>
       <c r="D301" t="n">
-        <v>0.2552790643580995</v>
+        <v>0.2552790643580994</v>
       </c>
     </row>
     <row r="302">
@@ -4661,12 +4661,12 @@
         <v>-1.130171353101175</v>
       </c>
       <c r="D302" t="n">
-        <v>0.01338550735845108</v>
+        <v>0.01338550735845102</v>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="n">
-        <v>-0.1329495316657654</v>
+        <v>-0.1329495316657653</v>
       </c>
       <c r="B303" t="n">
         <v>-0.1704520997088966</v>
@@ -4675,12 +4675,12 @@
         <v>-0.5097004840339641</v>
       </c>
       <c r="D303" t="n">
-        <v>0.9230482878044538</v>
+        <v>0.9230482878044537</v>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="n">
-        <v>-0.452509500621622</v>
+        <v>-0.4525095006216219</v>
       </c>
       <c r="B304" t="n">
         <v>-0.6175858692758488</v>
@@ -4689,7 +4689,7 @@
         <v>-0.4058547778966912</v>
       </c>
       <c r="D304" t="n">
-        <v>0.5751848774187601</v>
+        <v>0.57518487741876</v>
       </c>
     </row>
     <row r="305">
@@ -4700,7 +4700,7 @@
         <v>1.085124453025315</v>
       </c>
       <c r="C305" t="n">
-        <v>-0.3499383074147722</v>
+        <v>-0.3499383074147723</v>
       </c>
       <c r="D305" t="n">
         <v>-1.720086093690458</v>
@@ -4714,10 +4714,10 @@
         <v>0.7602841868547966</v>
       </c>
       <c r="C306" t="n">
-        <v>-0.2369062324216762</v>
+        <v>-0.2369062324216763</v>
       </c>
       <c r="D306" t="n">
-        <v>0.7826015880049032</v>
+        <v>0.7826015880049031</v>
       </c>
     </row>
     <row r="307">
@@ -4736,7 +4736,7 @@
     </row>
     <row r="308">
       <c r="A308" t="n">
-        <v>0.4160672563630607</v>
+        <v>0.4160672563630608</v>
       </c>
       <c r="B308" t="n">
         <v>-1.07419456997211</v>
@@ -4750,7 +4750,7 @@
     </row>
     <row r="309">
       <c r="A309" t="n">
-        <v>-0.2633135631143892</v>
+        <v>-0.2633135631143891</v>
       </c>
       <c r="B309" t="n">
         <v>-1.217529363678046</v>
@@ -4787,7 +4787,7 @@
         <v>0.1962410227804874</v>
       </c>
       <c r="D311" t="n">
-        <v>0.9321495919696174</v>
+        <v>0.9321495919696173</v>
       </c>
     </row>
     <row r="312">
@@ -4798,7 +4798,7 @@
         <v>0.7942720095116745</v>
       </c>
       <c r="C312" t="n">
-        <v>-0.1510347179921565</v>
+        <v>-0.1510347179921566</v>
       </c>
       <c r="D312" t="n">
         <v>-2.78901164033714</v>
@@ -4812,7 +4812,7 @@
         <v>-0.1602896221920095</v>
       </c>
       <c r="C313" t="n">
-        <v>-0.1799910662516384</v>
+        <v>-0.1799910662516385</v>
       </c>
       <c r="D313" t="n">
         <v>1.149992575586958</v>
@@ -4826,10 +4826,10 @@
         <v>1.065497205163172</v>
       </c>
       <c r="C314" t="n">
-        <v>-0.3735030973654438</v>
+        <v>-0.3735030973654439</v>
       </c>
       <c r="D314" t="n">
-        <v>-0.5490348632899229</v>
+        <v>-0.549034863289923</v>
       </c>
     </row>
     <row r="315">
@@ -4857,7 +4857,7 @@
         <v>-1.087030496188505</v>
       </c>
       <c r="D316" t="n">
-        <v>0.4828569235907751</v>
+        <v>0.482856923590775</v>
       </c>
     </row>
     <row r="317">
@@ -4871,7 +4871,7 @@
         <v>-0.6936352915267244</v>
       </c>
       <c r="D317" t="n">
-        <v>0.97571517168618</v>
+        <v>0.9757151716861799</v>
       </c>
     </row>
     <row r="318">
@@ -4882,10 +4882,10 @@
         <v>-0.2703229542038397</v>
       </c>
       <c r="C318" t="n">
-        <v>-0.3477416430365879</v>
+        <v>-0.347741643036588</v>
       </c>
       <c r="D318" t="n">
-        <v>0.4256343592816245</v>
+        <v>0.4256343592816244</v>
       </c>
     </row>
     <row r="319">
@@ -4913,7 +4913,7 @@
         <v>2.041089498697497</v>
       </c>
       <c r="D320" t="n">
-        <v>0.7331880432363599</v>
+        <v>0.7331880432363598</v>
       </c>
     </row>
     <row r="321">
@@ -4941,7 +4941,7 @@
         <v>-0.3387550133183885</v>
       </c>
       <c r="D322" t="n">
-        <v>0.8339711589172303</v>
+        <v>0.8339711589172302</v>
       </c>
     </row>
     <row r="323">
@@ -4955,7 +4955,7 @@
         <v>-0.3461439630034364</v>
       </c>
       <c r="D323" t="n">
-        <v>0.4971590448266729</v>
+        <v>0.4971590448266728</v>
       </c>
     </row>
     <row r="324">
@@ -4969,7 +4969,7 @@
         <v>1.027197787506268</v>
       </c>
       <c r="D324" t="n">
-        <v>0.7728465990101974</v>
+        <v>0.7728465990101973</v>
       </c>
     </row>
     <row r="325">
@@ -4983,7 +4983,7 @@
         <v>2.466648065076989</v>
       </c>
       <c r="D325" t="n">
-        <v>-0.263575726573712</v>
+        <v>-0.2635757265737121</v>
       </c>
     </row>
     <row r="326">
@@ -4997,7 +4997,7 @@
         <v>-1.171704041927959</v>
       </c>
       <c r="D326" t="n">
-        <v>-0.857875803524372</v>
+        <v>-0.8578758035243721</v>
       </c>
     </row>
     <row r="327">
@@ -5008,10 +5008,10 @@
         <v>-0.317280509665014</v>
       </c>
       <c r="C327" t="n">
-        <v>-0.2297184202812832</v>
+        <v>-0.2297184202812833</v>
       </c>
       <c r="D327" t="n">
-        <v>0.5699830546790574</v>
+        <v>0.5699830546790573</v>
       </c>
     </row>
     <row r="328">
@@ -5025,7 +5025,7 @@
         <v>1.539644044091288</v>
       </c>
       <c r="D328" t="n">
-        <v>0.501060537590071</v>
+        <v>0.5010605375900709</v>
       </c>
     </row>
     <row r="329">
@@ -5050,7 +5050,7 @@
         <v>1.672079078479916</v>
       </c>
       <c r="C330" t="n">
-        <v>-0.3239780462196467</v>
+        <v>-0.3239780462196468</v>
       </c>
       <c r="D330" t="n">
         <v>-2.88721521511374</v>
@@ -5081,7 +5081,7 @@
         <v>0.979675255229156</v>
       </c>
       <c r="D332" t="n">
-        <v>0.4880562321580564</v>
+        <v>0.4880562321580563</v>
       </c>
     </row>
     <row r="333">
@@ -5092,7 +5092,7 @@
         <v>-1.036701276816989</v>
       </c>
       <c r="C333" t="n">
-        <v>0.4917943488256343</v>
+        <v>0.4917943488256342</v>
       </c>
       <c r="D333" t="n">
         <v>0.2338231169145893</v>
@@ -5109,7 +5109,7 @@
         <v>-0.3555300709968834</v>
       </c>
       <c r="D334" t="n">
-        <v>0.9256479420880945</v>
+        <v>0.9256479420880944</v>
       </c>
     </row>
     <row r="335">
@@ -5120,7 +5120,7 @@
         <v>-1.091010667579623</v>
       </c>
       <c r="C335" t="n">
-        <v>0.4203124427472126</v>
+        <v>0.4203124427472125</v>
       </c>
       <c r="D335" t="n">
         <v>0.2942939919920801</v>
@@ -5137,7 +5137,7 @@
         <v>0.3070880867873259</v>
       </c>
       <c r="D336" t="n">
-        <v>0.532921136181955</v>
+        <v>0.5329211361819549</v>
       </c>
     </row>
     <row r="337">
@@ -5148,7 +5148,7 @@
         <v>-0.1792123890264865</v>
       </c>
       <c r="C337" t="n">
-        <v>-0.04738478883925238</v>
+        <v>-0.04738478883925243</v>
       </c>
       <c r="D337" t="n">
         <v>1.151903346627158</v>
@@ -5179,7 +5179,7 @@
         <v>-1.036711149848983</v>
       </c>
       <c r="D339" t="n">
-        <v>0.01992235565387245</v>
+        <v>0.01992235565387239</v>
       </c>
     </row>
     <row r="340">
@@ -5198,7 +5198,7 @@
     </row>
     <row r="341">
       <c r="A341" t="n">
-        <v>-0.04072395907540374</v>
+        <v>-0.04072395907540372</v>
       </c>
       <c r="B341" t="n">
         <v>0.5675510480117841</v>
@@ -5221,7 +5221,7 @@
         <v>1.397449355801607</v>
       </c>
       <c r="D342" t="n">
-        <v>0.8976903447630613</v>
+        <v>0.8976903447630612</v>
       </c>
     </row>
     <row r="343">
@@ -5235,7 +5235,7 @@
         <v>-0.7749060468235801</v>
       </c>
       <c r="D343" t="n">
-        <v>0.5316203033711662</v>
+        <v>0.5316203033711661</v>
       </c>
     </row>
     <row r="344">
@@ -5249,7 +5249,7 @@
         <v>-0.1901761307955805</v>
       </c>
       <c r="D344" t="n">
-        <v>-0.2070068470941036</v>
+        <v>-0.2070068470941037</v>
       </c>
     </row>
     <row r="345">
@@ -5268,7 +5268,7 @@
     </row>
     <row r="346">
       <c r="A346" t="n">
-        <v>0.04661868254703114</v>
+        <v>0.04661868254703116</v>
       </c>
       <c r="B346" t="n">
         <v>-0.8296075631792419</v>
@@ -5277,12 +5277,12 @@
         <v>0.359808031863749</v>
       </c>
       <c r="D346" t="n">
-        <v>0.04656252663013608</v>
+        <v>0.04656252663013602</v>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="n">
-        <v>-0.3192623258513131</v>
+        <v>-0.319262325851313</v>
       </c>
       <c r="B347" t="n">
         <v>-0.2934509308650012</v>
@@ -5319,7 +5319,7 @@
         <v>3.294808015740359</v>
       </c>
       <c r="D349" t="n">
-        <v>-0.1023167074705081</v>
+        <v>-0.1023167074705082</v>
       </c>
     </row>
     <row r="350">
@@ -5333,7 +5333,7 @@
         <v>1.041391618872997</v>
       </c>
       <c r="D350" t="n">
-        <v>0.7273350498395365</v>
+        <v>0.7273350498395363</v>
       </c>
     </row>
     <row r="351">
@@ -5347,7 +5347,7 @@
         <v>-0.6435023994580303</v>
       </c>
       <c r="D351" t="n">
-        <v>0.7032744197675429</v>
+        <v>0.7032744197675428</v>
       </c>
     </row>
     <row r="352">
@@ -5358,10 +5358,10 @@
         <v>0.2335830108337636</v>
       </c>
       <c r="C352" t="n">
-        <v>-0.3070013848608197</v>
+        <v>-0.3070013848608198</v>
       </c>
       <c r="D352" t="n">
-        <v>0.4678975976839453</v>
+        <v>0.4678975976839452</v>
       </c>
     </row>
     <row r="353">
@@ -5375,7 +5375,7 @@
         <v>0.5545129041751721</v>
       </c>
       <c r="D353" t="n">
-        <v>0.6050959867151557</v>
+        <v>0.6050959867151556</v>
       </c>
     </row>
     <row r="354">
@@ -5403,7 +5403,7 @@
         <v>0.2260037857612975</v>
       </c>
       <c r="D355" t="n">
-        <v>0.8430724630823939</v>
+        <v>0.8430724630823938</v>
       </c>
     </row>
     <row r="356">
@@ -5456,7 +5456,7 @@
         <v>-0.3155277744158925</v>
       </c>
       <c r="C359" t="n">
-        <v>-0.01345011154868116</v>
+        <v>-0.0134501115486812</v>
       </c>
       <c r="D359" t="n">
         <v>1.148685205927873</v>
@@ -5487,7 +5487,7 @@
         <v>-0.2552789701333227</v>
       </c>
       <c r="D361" t="n">
-        <v>0.5764852073950647</v>
+        <v>0.5764852073950646</v>
       </c>
     </row>
     <row r="362">
@@ -5498,7 +5498,7 @@
         <v>-0.1389130260087625</v>
       </c>
       <c r="C362" t="n">
-        <v>0.1301429837722044</v>
+        <v>0.1301429837722043</v>
       </c>
       <c r="D362" t="n">
         <v>1.056968195998268</v>
@@ -5506,7 +5506,7 @@
     </row>
     <row r="363">
       <c r="A363" t="n">
-        <v>0.03066567273493982</v>
+        <v>0.03066567273493985</v>
       </c>
       <c r="B363" t="n">
         <v>0.2921091269783424</v>
@@ -5543,7 +5543,7 @@
         <v>1.178971563959702</v>
       </c>
       <c r="D365" t="n">
-        <v>0.2747890423475112</v>
+        <v>0.2747890423475111</v>
       </c>
     </row>
     <row r="366">
@@ -5557,7 +5557,7 @@
         <v>0.7252584026852853</v>
       </c>
       <c r="D366" t="n">
-        <v>0.6272005906433654</v>
+        <v>0.6272005906433653</v>
       </c>
     </row>
     <row r="367">
@@ -5571,7 +5571,7 @@
         <v>-1.090643047685784</v>
       </c>
       <c r="D367" t="n">
-        <v>-0.7291501755529963</v>
+        <v>-0.7291501755529964</v>
       </c>
     </row>
     <row r="368">
@@ -5585,7 +5585,7 @@
         <v>-1.502823520133416</v>
       </c>
       <c r="D368" t="n">
-        <v>-0.796781413686395</v>
+        <v>-0.7967814136863951</v>
       </c>
     </row>
     <row r="369">
@@ -5599,21 +5599,21 @@
         <v>-0.112503942925692</v>
       </c>
       <c r="D369" t="n">
-        <v>-0.1842787284054075</v>
+        <v>-0.1842787284054076</v>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="n">
-        <v>0.3083086642058245</v>
+        <v>0.3083086642058246</v>
       </c>
       <c r="B370" t="n">
         <v>1.083718877898</v>
       </c>
       <c r="C370" t="n">
-        <v>-0.4060552162378305</v>
+        <v>-0.4060552162378306</v>
       </c>
       <c r="D370" t="n">
-        <v>-0.5587898522846289</v>
+        <v>-0.558789852284629</v>
       </c>
     </row>
     <row r="371">
@@ -5655,7 +5655,7 @@
         <v>-0.5516363802214124</v>
       </c>
       <c r="D373" t="n">
-        <v>-0.1049314467886767</v>
+        <v>-0.1049314467886768</v>
       </c>
     </row>
     <row r="374">
@@ -5669,12 +5669,12 @@
         <v>1.301588553812514</v>
       </c>
       <c r="D374" t="n">
-        <v>0.5556784192707382</v>
+        <v>0.5556784192707381</v>
       </c>
     </row>
     <row r="375">
       <c r="A375" t="n">
-        <v>-0.438650345122059</v>
+        <v>-0.4386503451220589</v>
       </c>
       <c r="B375" t="n">
         <v>-0.2825878672876682</v>
@@ -5683,7 +5683,7 @@
         <v>-0.4072531849278961</v>
       </c>
       <c r="D375" t="n">
-        <v>0.8222651721235834</v>
+        <v>0.8222651721235833</v>
       </c>
     </row>
     <row r="376">
@@ -5711,7 +5711,7 @@
         <v>0.7895618193368553</v>
       </c>
       <c r="D377" t="n">
-        <v>0.9588098763252517</v>
+        <v>0.9588098763252516</v>
       </c>
     </row>
     <row r="378">
@@ -5722,10 +5722,10 @@
         <v>0.276342977056293</v>
       </c>
       <c r="C378" t="n">
-        <v>-0.1482402346081321</v>
+        <v>-0.1482402346081322</v>
       </c>
       <c r="D378" t="n">
-        <v>0.6681665160762872</v>
+        <v>0.6681665160762871</v>
       </c>
     </row>
     <row r="379">
@@ -5778,10 +5778,10 @@
         <v>-0.2380839718288632</v>
       </c>
       <c r="C382" t="n">
-        <v>-0.1941709135480557</v>
+        <v>-0.1941709135480558</v>
       </c>
       <c r="D382" t="n">
-        <v>0.37426981671414</v>
+        <v>0.3742698167141399</v>
       </c>
     </row>
     <row r="383">
@@ -5809,7 +5809,7 @@
         <v>-0.4428006916611236</v>
       </c>
       <c r="D384" t="n">
-        <v>0.7806505902059621</v>
+        <v>0.7806505902059619</v>
       </c>
     </row>
     <row r="385">
@@ -5834,7 +5834,7 @@
         <v>0.0801043677150374</v>
       </c>
       <c r="C386" t="n">
-        <v>-0.3283713749760153</v>
+        <v>-0.3283713749760154</v>
       </c>
       <c r="D386" t="n">
         <v>1.373653354187223</v>
@@ -5851,7 +5851,7 @@
         <v>-0.1328624186216494</v>
       </c>
       <c r="D387" t="n">
-        <v>0.5647812319393547</v>
+        <v>0.5647812319393546</v>
       </c>
     </row>
     <row r="388">
@@ -5865,12 +5865,12 @@
         <v>-1.067056582426128</v>
       </c>
       <c r="D388" t="n">
-        <v>0.2442267623939947</v>
+        <v>0.2442267623939946</v>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="n">
-        <v>0.0956413514847767</v>
+        <v>0.09564135148477673</v>
       </c>
       <c r="B389" t="n">
         <v>1.482157089891533</v>
@@ -5884,16 +5884,16 @@
     </row>
     <row r="390">
       <c r="A390" t="n">
-        <v>-0.05969755406047676</v>
+        <v>-0.05969755406047673</v>
       </c>
       <c r="B390" t="n">
         <v>-0.3947243122520432</v>
       </c>
       <c r="C390" t="n">
-        <v>-0.1558289234308038</v>
+        <v>-0.1558289234308039</v>
       </c>
       <c r="D390" t="n">
-        <v>0.6909197764891964</v>
+        <v>0.6909197764891963</v>
       </c>
     </row>
     <row r="391">
@@ -5904,10 +5904,10 @@
         <v>-0.6515906265728147</v>
       </c>
       <c r="C391" t="n">
-        <v>-0.3723048956075398</v>
+        <v>-0.3723048956075399</v>
       </c>
       <c r="D391" t="n">
-        <v>0.5920901727796885</v>
+        <v>0.5920901727796883</v>
       </c>
     </row>
     <row r="392">
@@ -5921,7 +5921,7 @@
         <v>-0.9482385983414224</v>
       </c>
       <c r="D392" t="n">
-        <v>0.0894744215171564</v>
+        <v>0.08947442151715634</v>
       </c>
     </row>
     <row r="393">
@@ -5932,7 +5932,7 @@
         <v>1.662629549310739</v>
       </c>
       <c r="C393" t="n">
-        <v>0.1313316297487286</v>
+        <v>0.1313316297487285</v>
       </c>
       <c r="D393" t="n">
         <v>-1.450868510815948</v>
@@ -5940,7 +5940,7 @@
     </row>
     <row r="394">
       <c r="A394" t="n">
-        <v>0.1226140970548162</v>
+        <v>0.1226140970548163</v>
       </c>
       <c r="B394" t="n">
         <v>0.5447739570932487</v>
@@ -5963,7 +5963,7 @@
         <v>2.021325345989802</v>
       </c>
       <c r="D395" t="n">
-        <v>0.03681759432511555</v>
+        <v>0.03681759432511549</v>
       </c>
     </row>
     <row r="396">
@@ -5977,7 +5977,7 @@
         <v>-0.8653596749586809</v>
       </c>
       <c r="D396" t="n">
-        <v>0.1688015897545167</v>
+        <v>0.1688015897545166</v>
       </c>
     </row>
     <row r="397">
@@ -5991,7 +5991,7 @@
         <v>1.233695892447519</v>
       </c>
       <c r="D397" t="n">
-        <v>0.2448754188786942</v>
+        <v>0.2448754188786941</v>
       </c>
     </row>
     <row r="398">
@@ -6002,7 +6002,7 @@
         <v>-0.2202128461438591</v>
       </c>
       <c r="C398" t="n">
-        <v>0.1656858291486613</v>
+        <v>0.1656858291486612</v>
       </c>
       <c r="D398" t="n">
         <v>1.629193839089774</v>
@@ -6019,7 +6019,7 @@
         <v>0.1557105256593999</v>
       </c>
       <c r="D399" t="n">
-        <v>0.4789549279928927</v>
+        <v>0.4789549279928926</v>
       </c>
     </row>
     <row r="400">
@@ -6033,7 +6033,7 @@
         <v>-0.876943146533828</v>
       </c>
       <c r="D400" t="n">
-        <v>0.2565814056723412</v>
+        <v>0.2565814056723411</v>
       </c>
     </row>
     <row r="401">
@@ -6061,7 +6061,7 @@
         <v>2.092411036742715</v>
       </c>
       <c r="D402" t="n">
-        <v>0.2955913049614792</v>
+        <v>0.2955913049614791</v>
       </c>
     </row>
     <row r="403">
@@ -6075,7 +6075,7 @@
         <v>-0.5081016386616197</v>
       </c>
       <c r="D403" t="n">
-        <v>0.9789634824545201</v>
+        <v>0.97896348245452</v>
       </c>
     </row>
     <row r="404">
@@ -6089,7 +6089,7 @@
         <v>0.4993923603618474</v>
       </c>
       <c r="D404" t="n">
-        <v>0.3918237685597678</v>
+        <v>0.3918237685597677</v>
       </c>
     </row>
     <row r="405">
@@ -6103,7 +6103,7 @@
         <v>-0.2291194359362505</v>
       </c>
       <c r="D405" t="n">
-        <v>-0.04509414316135754</v>
+        <v>-0.0450941431613576</v>
       </c>
     </row>
     <row r="406">
